--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/phi-4/default/total_votes_file.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/phi-4/default/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D2">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="E2">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="G2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>282</v>
+        <v>305</v>
       </c>
       <c r="D3">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E3">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G3">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="H3">
         <v>426</v>
